--- a/config/excel/CfgSpawns.xlsx
+++ b/config/excel/CfgSpawns.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgSpawns" sheetId="1" r:id="R695f21432f8745ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgSpawns" sheetId="1" r:id="R5062c14a50c346a9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,6 +13,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="3">
+    <x:numFmt numFmtId="200" formatCode="0"/>
+    <x:numFmt numFmtId="201" formatCode="0.###"/>
+    <x:numFmt numFmtId="202" formatCode="General"/>
+  </x:numFmts>
   <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
@@ -34,7 +39,7 @@
       <x:name val="Microsoft YaHei"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -56,6 +61,36 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -63,7 +98,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -118,6 +153,42 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -353,212 +424,652 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="9" t="str">
+      <x:c r="A1" s="22" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="9" t="str">
-        <x:v>LayoutID</x:v>
-      </x:c>
-      <x:c r="C1" s="9" t="str">
-        <x:v>RoomType</x:v>
-      </x:c>
-      <x:c r="D1" s="9" t="str">
-        <x:v>IsStart</x:v>
-      </x:c>
-      <x:c r="E1" s="9" t="str">
+      <x:c r="B1" s="22" t="str">
+        <x:v>EncounterID</x:v>
+      </x:c>
+      <x:c r="C1" s="22" t="str">
         <x:v>EnemyID</x:v>
       </x:c>
-      <x:c r="F1" s="9" t="str">
+      <x:c r="D1" s="22" t="str">
         <x:v>Count</x:v>
       </x:c>
-      <x:c r="G1" s="9" t="str">
+      <x:c r="E1" s="22" t="str">
         <x:v>StartX</x:v>
       </x:c>
-      <x:c r="H1" s="9" t="str">
+      <x:c r="F1" s="22" t="str">
         <x:v>StartZ</x:v>
       </x:c>
-      <x:c r="I1" s="9" t="str">
+      <x:c r="G1" s="22" t="str">
         <x:v>StepX</x:v>
       </x:c>
-      <x:c r="J1" s="9" t="str">
+      <x:c r="H1" s="22" t="str">
         <x:v>StepZ</x:v>
       </x:c>
-      <x:c r="K1" s="9" t="str">
+      <x:c r="I1" s="22" t="str">
         <x:v>AlternateZ</x:v>
       </x:c>
+      <x:c r="J1" s="9"/>
+      <x:c r="K1" s="9"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="10" t="str">
+      <x:c r="A2" s="23" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="B2" s="10" t="str">
+      <x:c r="B2" s="23" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="C2" s="10" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="D2" s="10" t="str">
-        <x:v>bool</x:v>
-      </x:c>
-      <x:c r="E2" s="10" t="str">
+      <x:c r="C2" s="23" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="F2" s="10" t="str">
+      <x:c r="D2" s="23" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="G2" s="10" t="str">
+      <x:c r="E2" s="23" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="H2" s="10" t="str">
+      <x:c r="F2" s="23" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="I2" s="10" t="str">
+      <x:c r="G2" s="23" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="J2" s="10" t="str">
+      <x:c r="H2" s="23" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="K2" s="10" t="str">
+      <x:c r="I2" s="23" t="str">
         <x:v>number</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" ht="42" customHeight="1">
-      <x:c r="A3" s="12" t="str">
+      <x:c r="J2" s="10"/>
+      <x:c r="K2" s="10"/>
+    </x:row>
+    <x:row r="3" ht="56" customHeight="1">
+      <x:c r="A3" s="24" t="str">
         <x:v># 刷怪组编号</x:v>
       </x:c>
-      <x:c r="B3" s="12" t="str">
-        <x:v>所属布局</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="str">
-        <x:v>房间类型</x:v>
-      </x:c>
-      <x:c r="D3" s="12" t="str">
-        <x:v>仅起始房间</x:v>
-      </x:c>
-      <x:c r="E3" s="12" t="str">
+      <x:c r="B3" s="24" t="str">
+        <x:v>所属遭遇组编号。</x:v>
+      </x:c>
+      <x:c r="C3" s="24" t="str">
         <x:v>敌人编号</x:v>
       </x:c>
-      <x:c r="F3" s="12" t="str">
+      <x:c r="D3" s="24" t="str">
         <x:v>敌人数量</x:v>
       </x:c>
-      <x:c r="G3" s="12" t="str">
+      <x:c r="E3" s="24" t="str">
         <x:v>首个敌人X</x:v>
       </x:c>
-      <x:c r="H3" s="12" t="str">
+      <x:c r="F3" s="24" t="str">
         <x:v>首个敌人Z</x:v>
       </x:c>
-      <x:c r="I3" s="12" t="str">
+      <x:c r="G3" s="24" t="str">
         <x:v>后续敌人X间距</x:v>
       </x:c>
-      <x:c r="J3" s="12" t="str">
+      <x:c r="H3" s="24" t="str">
         <x:v>后续敌人Z间距</x:v>
       </x:c>
-      <x:c r="K3" s="12" t="str">
+      <x:c r="I3" s="24" t="str">
         <x:v>奇数敌人额外Z偏移</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" ht="48" customHeight="1">
-      <x:c r="A4" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B4" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="13" t="str">
-        <x:v>Mob</x:v>
-      </x:c>
-      <x:c r="D4" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E4" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F4" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G4" s="6" t="n">
+      <x:c r="J3" s="12"/>
+      <x:c r="K3" s="12"/>
+    </x:row>
+    <x:row r="4" ht="36" customHeight="1">
+      <x:c r="A4" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B4" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D4" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E4" s="25" t="n">
         <x:v>-1.5</x:v>
       </x:c>
-      <x:c r="H4" s="6" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="I4" s="6" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="J4" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K4" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="48" customHeight="1">
-      <x:c r="A5" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B5" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="13" t="str">
-        <x:v>Mob</x:v>
-      </x:c>
-      <x:c r="D5" s="7" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E5" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F5" s="6" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G5" s="6" t="n">
+      <x:c r="F4" s="25" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G4" s="25" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H4" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I4" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J4" s="6"/>
+      <x:c r="K4" s="6"/>
+    </x:row>
+    <x:row r="5" ht="36" customHeight="1">
+      <x:c r="A5" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B5" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C5" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D5" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E5" s="25" t="n">
         <x:v>-3</x:v>
       </x:c>
-      <x:c r="H5" s="6" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="I5" s="6" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="J5" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K5" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="48" customHeight="1">
-      <x:c r="A6" s="6" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B6" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="13" t="str">
-        <x:v>Boss</x:v>
-      </x:c>
-      <x:c r="D6" s="7" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E6" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F6" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G6" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H6" s="6" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="I6" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J6" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K6" s="6" t="n">
+      <x:c r="F5" s="25" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G5" s="25" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H5" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I5" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J5" s="6"/>
+      <x:c r="K5" s="6"/>
+    </x:row>
+    <x:row r="6" ht="36" customHeight="1">
+      <x:c r="A6" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B6" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C6" s="20" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D6" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E6" s="25" t="n">
+        <x:v>-2</x:v>
+      </x:c>
+      <x:c r="F6" s="25" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G6" s="25" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H6" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I6" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J6" s="6"/>
+      <x:c r="K6" s="6"/>
+    </x:row>
+    <x:row r="7" ht="36" customHeight="1">
+      <x:c r="A7" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B7" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C7" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D7" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E7" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F7" s="25" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H7" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I7" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="36" customHeight="1">
+      <x:c r="A8" s="19" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B8" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C8" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D8" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E8" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F8" s="25" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G8" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H8" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I8" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="36" customHeight="1">
+      <x:c r="A9" s="19" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B9" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C9" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D9" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E9" s="25" t="n">
+        <x:v>-3</x:v>
+      </x:c>
+      <x:c r="F9" s="25" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G9" s="25" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H9" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I9" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="36" customHeight="1">
+      <x:c r="A10" s="19" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B10" s="19" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C10" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D10" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E10" s="25" t="n">
+        <x:v>-2</x:v>
+      </x:c>
+      <x:c r="F10" s="25" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G10" s="25" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H10" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I10" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="36" customHeight="1">
+      <x:c r="A11" s="19" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B11" s="19" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C11" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D11" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E11" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F11" s="25" t="n">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="G11" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H11" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I11" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="36" customHeight="1">
+      <x:c r="A12" s="19" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B12" s="19" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C12" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D12" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E12" s="25" t="n">
+        <x:v>-3</x:v>
+      </x:c>
+      <x:c r="F12" s="25" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G12" s="25" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H12" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I12" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="36" customHeight="1">
+      <x:c r="A13" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B13" s="19" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C13" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D13" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E13" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F13" s="25" t="n">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="G13" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H13" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I13" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="36" customHeight="1">
+      <x:c r="A14" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B14" s="19" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C14" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D14" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E14" s="25" t="n">
+        <x:v>-3</x:v>
+      </x:c>
+      <x:c r="F14" s="25" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G14" s="25" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H14" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I14" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="36" customHeight="1">
+      <x:c r="A15" s="19" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B15" s="19" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C15" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D15" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E15" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F15" s="25" t="n">
+        <x:v>-5</x:v>
+      </x:c>
+      <x:c r="G15" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H15" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I15" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="36" customHeight="1">
+      <x:c r="A16" s="19" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B16" s="19" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C16" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D16" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E16" s="25" t="n">
+        <x:v>-3</x:v>
+      </x:c>
+      <x:c r="F16" s="25" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G16" s="25" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H16" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I16" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="36" customHeight="1">
+      <x:c r="A17" s="19" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B17" s="19" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C17" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D17" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E17" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F17" s="25" t="n">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="G17" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H17" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I17" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="36" customHeight="1">
+      <x:c r="A18" s="19" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B18" s="19" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C18" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D18" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E18" s="25" t="n">
+        <x:v>-3</x:v>
+      </x:c>
+      <x:c r="F18" s="25" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G18" s="25" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H18" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I18" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="36" customHeight="1">
+      <x:c r="A19" s="19" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B19" s="19" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C19" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D19" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E19" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F19" s="25" t="n">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="G19" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H19" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I19" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="36" customHeight="1">
+      <x:c r="A20" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B20" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C20" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D20" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E20" s="25" t="n">
+        <x:v>-3</x:v>
+      </x:c>
+      <x:c r="F20" s="25" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G20" s="25" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H20" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I20" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="36" customHeight="1">
+      <x:c r="A21" s="19" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B21" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C21" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D21" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E21" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F21" s="25" t="n">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="G21" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H21" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I21" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="36" customHeight="1">
+      <x:c r="A22" s="19" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B22" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C22" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D22" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E22" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F22" s="25" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G22" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H22" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I22" s="25" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>

--- a/config/excel/CfgSpawns.xlsx
+++ b/config/excel/CfgSpawns.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgSpawns" sheetId="1" r:id="R5062c14a50c346a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgSpawns" sheetId="1" r:id="R08b385eb7c8d4389"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,7 +18,7 @@
     <x:numFmt numFmtId="201" formatCode="0.###"/>
     <x:numFmt numFmtId="202" formatCode="General"/>
   </x:numFmts>
-  <x:fonts count="4">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -37,6 +37,11 @@
       <x:sz val="10"/>
       <x:color rgb="FF0000FF"/>
       <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
   <x:fills count="11">
@@ -98,7 +103,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -191,6 +196,7 @@
     <x:xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1073,6 +1079,471 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
+    <x:row r="23" ht="36" customHeight="1">
+      <x:c r="A23" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B23" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C23" s="26" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E23" t="n">
+        <x:v>-3</x:v>
+      </x:c>
+      <x:c r="F23" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J23"/>
+      <x:c r="K23"/>
+    </x:row>
+    <x:row r="24" ht="36" customHeight="1">
+      <x:c r="A24" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B24" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C24" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F24" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H24" t="n">
+        <x:v>-8</x:v>
+      </x:c>
+      <x:c r="I24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J24"/>
+      <x:c r="K24"/>
+    </x:row>
+    <x:row r="25" ht="36" customHeight="1">
+      <x:c r="A25" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B25" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C25" s="26" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E25" t="n">
+        <x:v>-3</x:v>
+      </x:c>
+      <x:c r="F25" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J25"/>
+      <x:c r="K25"/>
+    </x:row>
+    <x:row r="26" ht="36" customHeight="1">
+      <x:c r="A26" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B26" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C26" s="26" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F26" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J26"/>
+      <x:c r="K26"/>
+    </x:row>
+    <x:row r="27" ht="36" customHeight="1">
+      <x:c r="A27" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B27" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C27" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F27" t="n">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="G27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J27"/>
+      <x:c r="K27"/>
+    </x:row>
+    <x:row r="28" ht="36" customHeight="1">
+      <x:c r="A28" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B28" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C28" s="26" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E28" t="n">
+        <x:v>-3</x:v>
+      </x:c>
+      <x:c r="F28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G28" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H28" t="n">
+        <x:v>-8</x:v>
+      </x:c>
+      <x:c r="I28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J28"/>
+      <x:c r="K28"/>
+    </x:row>
+    <x:row r="29" ht="36" customHeight="1">
+      <x:c r="A29" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B29" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C29" s="26" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E29" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F29" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G29" t="n">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="H29" t="n">
+        <x:v>-8</x:v>
+      </x:c>
+      <x:c r="I29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J29"/>
+      <x:c r="K29"/>
+    </x:row>
+    <x:row r="30" ht="36" customHeight="1">
+      <x:c r="A30" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B30" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C30" s="26" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E30" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F30" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G30" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H30" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I30" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J30"/>
+      <x:c r="K30"/>
+    </x:row>
+    <x:row r="31" ht="36" customHeight="1">
+      <x:c r="A31" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B31" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C31" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E31" t="n">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="F31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G31" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J31"/>
+      <x:c r="K31"/>
+    </x:row>
+    <x:row r="32" ht="36" customHeight="1">
+      <x:c r="A32" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B32" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C32" s="26" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F32" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+    </x:row>
+    <x:row r="33" ht="36" customHeight="1">
+      <x:c r="A33" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B33" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C33" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E33" t="n">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="F33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J33"/>
+      <x:c r="K33"/>
+    </x:row>
+    <x:row r="34" ht="36" customHeight="1">
+      <x:c r="A34" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B34" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C34" s="26" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E34" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J34"/>
+      <x:c r="K34"/>
+    </x:row>
+    <x:row r="35" ht="36" customHeight="1">
+      <x:c r="A35" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B35" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C35" s="26" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D35" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E35" t="n">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="F35" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G35" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H35" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I35" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J35"/>
+      <x:c r="K35"/>
+    </x:row>
+    <x:row r="36" ht="36" customHeight="1">
+      <x:c r="A36" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B36" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C36" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D36" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F36" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J36"/>
+      <x:c r="K36"/>
+    </x:row>
+    <x:row r="37" ht="36" customHeight="1">
+      <x:c r="A37" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B37" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C37" s="26" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F37" t="n">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="G37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J37"/>
+      <x:c r="K37"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
